--- a/public/Databricks Ideas.xlsx
+++ b/public/Databricks Ideas.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Enterprise Problem Bank" sheetId="1" r:id="rId1"/>
-    <sheet name="Growth Industry Bank" sheetId="2" r:id="rId2"/>
+    <sheet name="Build Queue" sheetId="1" r:id="rId1"/>
+    <sheet name="Enterprise Problem Bank" sheetId="2" r:id="rId2"/>
+    <sheet name="Growth Industry Bank" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Enterprise Problem Bank'!A1:H36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Growth Industry Bank'!A1:H15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Enterprise Problem Bank'!A1:H36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Growth Industry Bank'!A1:H15</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -402,6 +403,209 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H7"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="55.83203125" customWidth="1"/>
+    <col min="7" max="7" width="45.83203125" customWidth="1"/>
+    <col min="8" max="8" width="70.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sprint</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Industry</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Question</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Dataset</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Dataset URL</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Backend</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Frontend</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Post Angle</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Energy &amp; Grid</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Does the AI data-center energy story show up in real grid demand?</v>
+      </c>
+      <c r="D2" t="str">
+        <v>EIA Open Data API</v>
+      </c>
+      <c r="E2" t="str">
+        <v>https://www.eia.gov/opendata/</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Ingest 5 years of hourly demand by region. Bronze to silver to gold with a clean regional daily table.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>React dashboard: region selector, demand trend, year-over-year delta.</v>
+      </c>
+      <c r="H2" t="str">
+        <v>I pulled 5 years of US grid demand to check the data-center story. Here is what it actually says.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Energy &amp; Grid</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Which regions are absorbing load growth, and at what carbon cost?</v>
+      </c>
+      <c r="D3" t="str">
+        <v>EIA + EPA eGRID</v>
+      </c>
+      <c r="E3" t="str">
+        <v>https://www.epa.gov/egrid/download-data</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Join plant-level emissions to regional demand. Incremental refresh on the eGRID table.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Map view: demand growth vs carbon intensity per region.</v>
+      </c>
+      <c r="H3" t="str">
+        <v>The load is growing where the grid is dirtiest.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Green Energy</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Is renewable build-out keeping pace with demand growth?</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Our World in Data energy datasets</v>
+      </c>
+      <c r="E4" t="str">
+        <v>https://github.com/owid/energy-data</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Country-level comparison pipeline. Practice schema evolution on a changing CSV.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Comparison chart with country selector.</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Renewables are growing fast. Demand is growing faster.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Energy &amp; Grid</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Can a simple model beat the naive forecast for regional load?</v>
+      </c>
+      <c r="D5" t="str">
+        <v>EIA hourly demand</v>
+      </c>
+      <c r="E5" t="str">
+        <v>https://www.eia.gov/opendata/</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Feature engineering on the gold table, baseline vs model, serve predictions in a gold table.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Forecast vs actual dashboard with error bands.</v>
+      </c>
+      <c r="H5" t="str">
+        <v>My model lost to a 7-day moving average three times before it won.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Green Energy</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Where does wind resource quality diverge from actual generation?</v>
+      </c>
+      <c r="D6" t="str">
+        <v>NREL WIND Toolkit + EIA</v>
+      </c>
+      <c r="E6" t="str">
+        <v>https://www.nrel.gov/grid/wind-toolkit.html</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Spatial join of resource data to generation. Larger volume, partitioning matters here.</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Site explorer with resource vs output.</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Great wind resource does not guarantee great generation. Here is the gap.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>AI Infrastructure</v>
+      </c>
+      <c r="C7" t="str">
+        <v>What would training-run growth do to regional grid capacity?</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Epoch AI + EIA</v>
+      </c>
+      <c r="E7" t="str">
+        <v>https://epoch.ai/data</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Combine compute-trend data with regional capacity headroom. Scenario table in gold.</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Scenario tool: pick a growth rate, see which regions run out of headroom first.</v>
+      </c>
+      <c r="H7" t="str">
+        <v>If training compute keeps this trajectory, three regions run out of headroom first.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H36"/>
   <sheetData>
     <row r="1">
@@ -1348,7 +1552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H15"/>
   <sheetData>
